--- a/data/trans_camb/P1402-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P1402-Edad-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,05</t>
+          <t>0,04</t>
         </is>
       </c>
     </row>
@@ -677,22 +677,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 1,46</t>
+          <t>-0,2; 1,49</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,7</t>
+          <t>-0,4; 0,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 0,0</t>
+          <t>-0,83; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,02</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -707,17 +707,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,02; 1,13</t>
+          <t>0,01; 1,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,36</t>
+          <t>-0,2; 0,38</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,57</t>
+          <t>-0,2; 0,48</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>41,61%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>-0,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,35</t>
+          <t>0,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,09</t>
+          <t>0,08; 2,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 0,87</t>
+          <t>-0,49; 0,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,43</t>
+          <t>0,0; 3,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 2,24</t>
+          <t>-0,17; 2,3</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,46</t>
+          <t>-0,58; 1,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,17</t>
+          <t>-1,16; 0,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,85</t>
+          <t>0,27; 1,75</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 0,85</t>
+          <t>-0,3; 0,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 1,41</t>
+          <t>-0,27; 1,56</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>462,76%</t>
+          <t>400,73%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-67,42%</t>
+          <t>-67,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,62; —</t>
+          <t>-55,59; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-79,98; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 1432,11</t>
+          <t>-7,34; 1553,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-55,85; 787,65</t>
+          <t>-63,8; 885,04</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-97,57; 1275,66</t>
+          <t>-100,0; 1535,4</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-0,68</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,22</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,76</t>
+          <t>-3,62; -0,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,39; 1,02</t>
+          <t>-2,44; 0,96</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 1,06</t>
+          <t>-2,18; 1,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 1,96</t>
+          <t>-0,43; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,23</t>
+          <t>-1,09; 1,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,28</t>
+          <t>-0,53; 2,01</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 0,35</t>
+          <t>-1,59; 0,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,77</t>
+          <t>-1,24; 0,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,79</t>
+          <t>-0,85; 1,24</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-26,98%</t>
+          <t>-11,86%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>71,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-12,38%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-94,97; -28,36</t>
+          <t>-95,1; -23,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 67,68</t>
+          <t>-68,72; 66,13</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,47; 74,58</t>
+          <t>-61,78; 83,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,64; 394,45</t>
+          <t>-34,62; 402,67</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-65,74; 233,32</t>
+          <t>-67,89; 246,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-52,4; 268,04</t>
+          <t>-35,49; 365,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,33; 30,24</t>
+          <t>-63,82; 22,8</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-53,14; 67,38</t>
+          <t>-55,46; 56,49</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-54,1; 65,8</t>
+          <t>-37,35; 100,67</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,58</t>
+          <t>2,57</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,01</t>
+          <t>-0,92</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,11</t>
+          <t>0,78</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 2,52</t>
+          <t>-2,56; 2,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 3,83</t>
+          <t>-1,44; 3,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 3,75</t>
+          <t>-0,06; 5,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 1,81</t>
+          <t>-3,11; 1,51</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 1,51</t>
+          <t>-2,92; 1,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 0,81</t>
+          <t>-3,37; 0,79</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 1,38</t>
+          <t>-1,9; 1,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,04</t>
+          <t>-1,54; 1,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,62</t>
+          <t>-0,85; 2,48</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-24,79%</t>
+          <t>-22,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,59%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,23; 92,01</t>
+          <t>-44,57; 71,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-24,84; 126,14</t>
+          <t>-28,2; 114,68</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 100,4</t>
+          <t>-3,1; 177,43</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,64; 63,79</t>
+          <t>-58,15; 56,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-53,48; 53,05</t>
+          <t>-54,73; 66,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,51; 35,06</t>
+          <t>-55,31; 30,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-39,03; 39,74</t>
+          <t>-36,83; 45,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 59,84</t>
+          <t>-30,56; 58,83</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-45,17; 46,12</t>
+          <t>-16,13; 75,15</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,44</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-4,44</t>
+          <t>-4,41</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,48</t>
+          <t>-1,5</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 4,99</t>
+          <t>-4,16; 4,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 6,32</t>
+          <t>-2,46; 6,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 5,44</t>
+          <t>-2,9; 5,32</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,16</t>
+          <t>-5,39; 3,61</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 5,08</t>
+          <t>-4,15; 4,49</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -1,4</t>
+          <t>-8,27; -0,78</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,08</t>
+          <t>-3,22; 2,78</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 3,97</t>
+          <t>-2,54; 4,18</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 1,2</t>
+          <t>-4,01; 1,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-36,15%</t>
+          <t>-35,89%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-12,41%</t>
+          <t>-12,62%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-28,68; 55,9</t>
+          <t>-30,73; 48,21</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,31; 69,84</t>
+          <t>-18,93; 68,54</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 59,43</t>
+          <t>-21,49; 56,65</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,24; 31,05</t>
+          <t>-36,97; 33,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-28,15; 49,75</t>
+          <t>-28,21; 43,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-53,98; -13,1</t>
+          <t>-55,25; -7,51</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 30,42</t>
+          <t>-24,11; 27,3</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-16,19; 39,17</t>
+          <t>-19,29; 40,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,65; 11,47</t>
+          <t>-29,93; 10,96</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3,38</t>
+          <t>2,6</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-11,13</t>
+          <t>-5,28</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-5,45</t>
+          <t>-1,56</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>3,89; 17,85</t>
+          <t>3,99; 18,33</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2,36; 15,21</t>
+          <t>2,09; 15,03</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 8,52</t>
+          <t>-3,13; 7,92</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 9,57</t>
+          <t>-3,49; 9,25</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 6,92</t>
+          <t>-5,26; 6,58</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-21,57; -3,78</t>
+          <t>-10,36; -0,35</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,1; 11,43</t>
+          <t>1,81; 11,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 9,25</t>
+          <t>-0,1; 8,81</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-14,78; -0,09</t>
+          <t>-5,12; 2,32</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-49,93%</t>
+          <t>-23,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-25,93%</t>
+          <t>-7,42%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>17,86; 111,54</t>
+          <t>18,21; 107,54</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>11,31; 91,13</t>
+          <t>9,36; 92,01</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 52,04</t>
+          <t>-14,03; 48,83</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,15; 49,04</t>
+          <t>-13,73; 50,11</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-21,85; 36,01</t>
+          <t>-21,62; 33,94</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-79,24; -17,94</t>
+          <t>-39,31; -0,13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,93; 60,98</t>
+          <t>7,49; 59,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 49,76</t>
+          <t>-0,54; 46,1</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-65,4; -0,89</t>
+          <t>-22,19; 12,59</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9,56</t>
+          <t>9,51</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,19</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,24</t>
+          <t>8,1</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 16,27</t>
+          <t>0,16; 16,02</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>6,8; 21,51</t>
+          <t>6,51; 21,64</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3,27; 16,58</t>
+          <t>2,36; 16,12</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3,35; 16,7</t>
+          <t>3,26; 16,52</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,71; 13,96</t>
+          <t>-0,67; 13,42</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,87; 13,34</t>
+          <t>1,6; 12,79</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,68; 14,45</t>
+          <t>3,74; 14,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,62</t>
+          <t>4,17; 14,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,4</t>
+          <t>3,64; 12,51</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 100,02</t>
+          <t>0,55; 95,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>25,82; 134,61</t>
+          <t>25,64; 132,59</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,9; 107,76</t>
+          <t>8,48; 98,85</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11,91; 93,16</t>
+          <t>12,11; 91,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,69; 77,74</t>
+          <t>-2,6; 74,92</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>6,51; 75,39</t>
+          <t>5,83; 73,85</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,39; 78,89</t>
+          <t>14,93; 75,89</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>18,52; 78,66</t>
+          <t>16,58; 81,9</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>15,27; 69,39</t>
+          <t>15,13; 69,85</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>3,03</t>
+          <t>3,65</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>1,7</t>
+          <t>2,31</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,07</t>
+          <t>0,62; 3,06</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,55</t>
+          <t>1,86; 4,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,27; 4,45</t>
+          <t>2,41; 4,83</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,16</t>
+          <t>0,58; 3,12</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>0,29; 2,89</t>
+          <t>0,29; 3,12</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,58</t>
+          <t>-0,05; 2,16</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,79</t>
+          <t>0,95; 2,68</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,23</t>
+          <t>1,44; 3,17</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,69</t>
+          <t>1,46; 3,07</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>27,26%</t>
+          <t>37,13%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>8,88; 60,65</t>
+          <t>9,71; 58,84</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>30,48; 88,73</t>
+          <t>30,07; 84,61</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20,49; 83,89</t>
+          <t>38,54; 92,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>8,86; 51,2</t>
+          <t>7,9; 50,77</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,73; 45,97</t>
+          <t>3,61; 50,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-17,19; 25,61</t>
+          <t>-0,5; 35,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>15,27; 47,76</t>
+          <t>14,23; 45,68</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>21,52; 55,8</t>
+          <t>21,24; 53,77</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>9,21; 46,0</t>
+          <t>22,0; 53,06</t>
         </is>
       </c>
     </row>
